--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.766024</v>
+        <v>0.626995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.476308</v>
+        <v>0.379168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.91018</v>
+        <v>0.77646</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.865683</v>
+        <v>0.770159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.63929</v>
+        <v>0.457888</v>
       </c>
       <c r="E3" t="n">
-        <v>1.126038</v>
+        <v>1.015082</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.38559</v>
+        <v>0.298671</v>
       </c>
       <c r="D4" t="n">
-        <v>0.28066</v>
+        <v>0.22457</v>
       </c>
       <c r="E4" t="n">
-        <v>0.684151</v>
+        <v>0.358501</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.601285</v>
+        <v>0.35213</v>
       </c>
       <c r="D5" t="n">
-        <v>0.357725</v>
+        <v>0.271123</v>
       </c>
       <c r="E5" t="n">
-        <v>1.049405</v>
+        <v>0.5359080000000001</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.626995</v>
+        <v>0.63491</v>
       </c>
       <c r="D2" t="n">
-        <v>0.379168</v>
+        <v>0.388335</v>
       </c>
       <c r="E2" t="n">
-        <v>0.77646</v>
+        <v>0.782212</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.770159</v>
+        <v>0.774709</v>
       </c>
       <c r="D3" t="n">
-        <v>0.457888</v>
+        <v>0.5132060000000001</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.298671</v>
+        <v>0.280086</v>
       </c>
       <c r="D4" t="n">
-        <v>0.22457</v>
+        <v>0.222955</v>
       </c>
       <c r="E4" t="n">
-        <v>0.358501</v>
+        <v>0.364926</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.35213</v>
+        <v>0.357118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.271123</v>
+        <v>0.266924</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5359080000000001</v>
+        <v>0.537914</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63491</v>
+        <v>0.654959</v>
       </c>
       <c r="D2" t="n">
-        <v>0.388335</v>
+        <v>0.401948</v>
       </c>
       <c r="E2" t="n">
-        <v>0.782212</v>
+        <v>0.76535</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.774709</v>
+        <v>0.744555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5132060000000001</v>
+        <v>0.46057</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.280086</v>
+        <v>0.339415</v>
       </c>
       <c r="D4" t="n">
-        <v>0.222955</v>
+        <v>0.230104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.364926</v>
+        <v>0.394741</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.357118</v>
+        <v>0.388032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.266924</v>
+        <v>0.279099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.537914</v>
+        <v>0.635779</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.654959</v>
+        <v>0.67306</v>
       </c>
       <c r="D2" t="n">
-        <v>0.401948</v>
+        <v>0.409011</v>
       </c>
       <c r="E2" t="n">
-        <v>0.76535</v>
+        <v>0.780574</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.744555</v>
+        <v>0.742665</v>
       </c>
       <c r="D3" t="n">
-        <v>0.46057</v>
+        <v>0.530887</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.339415</v>
+        <v>0.335623</v>
       </c>
       <c r="D4" t="n">
-        <v>0.230104</v>
+        <v>0.221018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.394741</v>
+        <v>0.391022</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.388032</v>
+        <v>0.384908</v>
       </c>
       <c r="D5" t="n">
-        <v>0.279099</v>
+        <v>0.286169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.635779</v>
+        <v>0.632473</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.67306</v>
+        <v>0.673009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.409011</v>
+        <v>0.40829</v>
       </c>
       <c r="E2" t="n">
-        <v>0.780574</v>
+        <v>0.774407</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.742665</v>
+        <v>0.741044</v>
       </c>
       <c r="D3" t="n">
-        <v>0.530887</v>
+        <v>0.528996</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.335623</v>
+        <v>0.25364</v>
       </c>
       <c r="D4" t="n">
-        <v>0.221018</v>
+        <v>0.18884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.391022</v>
+        <v>0.351256</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.384908</v>
+        <v>0.314223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.286169</v>
+        <v>0.214456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.632473</v>
+        <v>0.375924</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.673009</v>
+        <v>0.672434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.40829</v>
+        <v>0.35577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.774407</v>
+        <v>0.76535</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.741044</v>
+        <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.528996</v>
+        <v>0.440642</v>
       </c>
       <c r="E3" t="n">
-        <v>1.015082</v>
+        <v>0.838984</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.25364</v>
+        <v>0.230509</v>
       </c>
       <c r="D4" t="n">
-        <v>0.18884</v>
+        <v>0.174893</v>
       </c>
       <c r="E4" t="n">
-        <v>0.351256</v>
+        <v>0.3128</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.314223</v>
+        <v>0.277584</v>
       </c>
       <c r="D5" t="n">
-        <v>0.214456</v>
+        <v>0.189777</v>
       </c>
       <c r="E5" t="n">
-        <v>0.375924</v>
+        <v>0.347132</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.230509</v>
+        <v>0.232207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.174893</v>
+        <v>0.17631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3128</v>
+        <v>0.313884</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.277584</v>
+        <v>0.279905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.189777</v>
+        <v>0.191128</v>
       </c>
       <c r="E5" t="n">
-        <v>0.347132</v>
+        <v>0.351465</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.672434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35577</v>
+        <v>0.389014</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.440642</v>
+        <v>0.419404</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.232207</v>
+        <v>0.265808</v>
       </c>
       <c r="D4" t="n">
-        <v>0.17631</v>
+        <v>0.204105</v>
       </c>
       <c r="E4" t="n">
-        <v>0.313884</v>
+        <v>0.336573</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.279905</v>
+        <v>0.30141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.191128</v>
+        <v>0.227054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.351465</v>
+        <v>0.406597</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.672434</v>
+        <v>0.634074</v>
       </c>
       <c r="D2" t="n">
-        <v>0.389014</v>
+        <v>0.35577</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.419404</v>
+        <v>0.410903</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.265808</v>
+        <v>0.264434</v>
       </c>
       <c r="D4" t="n">
-        <v>0.204105</v>
+        <v>0.198577</v>
       </c>
       <c r="E4" t="n">
-        <v>0.336573</v>
+        <v>0.336419</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.30141</v>
+        <v>0.298916</v>
       </c>
       <c r="D5" t="n">
-        <v>0.227054</v>
+        <v>0.231994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.406597</v>
+        <v>0.404876</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>tail_support_count</t>
+          <t>tail_support_at_or_beyond_var_incl_atom</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.634074</v>
+        <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35577</v>
+        <v>0.303016</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -503,13 +503,13 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.410903</v>
+        <v>0.40983</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.264434</v>
+        <v>0.260987</v>
       </c>
       <c r="D4" t="n">
-        <v>0.198577</v>
+        <v>0.196313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.336419</v>
+        <v>0.302565</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.298916</v>
+        <v>0.295407</v>
       </c>
       <c r="D5" t="n">
-        <v>0.231994</v>
+        <v>0.221134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.404876</v>
+        <v>0.33963</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
       <c r="D4" t="n">
-        <v>0.196313</v>
+        <v>0.194423</v>
       </c>
       <c r="E4" t="n">
-        <v>0.302565</v>
+        <v>0.303891</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.221134</v>
+        <v>0.21942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33963</v>
+        <v>0.34116</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.257932</v>
+        <v>0.256726</v>
       </c>
       <c r="D4" t="n">
-        <v>0.194423</v>
+        <v>0.193669</v>
       </c>
       <c r="E4" t="n">
-        <v>0.303891</v>
+        <v>0.304581</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.295159</v>
+        <v>0.295054</v>
       </c>
       <c r="D5" t="n">
-        <v>0.21942</v>
+        <v>0.219982</v>
       </c>
       <c r="E5" t="n">
-        <v>0.34116</v>
+        <v>0.341841</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.303016</v>
+        <v>0.235662</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.40983</v>
+        <v>0.389014</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.256726</v>
+        <v>0.263619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.193669</v>
+        <v>0.187043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.304581</v>
+        <v>0.330368</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.295054</v>
+        <v>0.330368</v>
       </c>
       <c r="D5" t="n">
-        <v>0.219982</v>
+        <v>0.207966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.341841</v>
+        <v>0.359432</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
       <c r="D4" t="n">
-        <v>0.187043</v>
+        <v>0.187097</v>
       </c>
       <c r="E4" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
       <c r="D5" t="n">
-        <v>0.207966</v>
+        <v>0.207983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.359432</v>
+        <v>0.35942</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.235662</v>
+        <v>0.229443</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.389014</v>
+        <v>0.371876</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.263815</v>
+        <v>0.266966</v>
       </c>
       <c r="D4" t="n">
-        <v>0.187097</v>
+        <v>0.183821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33048</v>
+        <v>0.334027</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.33048</v>
+        <v>0.334027</v>
       </c>
       <c r="D5" t="n">
-        <v>0.207983</v>
+        <v>0.198512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.35942</v>
+        <v>0.362633</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
       <c r="D4" t="n">
-        <v>0.183821</v>
+        <v>0.184192</v>
       </c>
       <c r="E4" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
       <c r="D5" t="n">
-        <v>0.198512</v>
+        <v>0.198508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.362633</v>
+        <v>0.362846</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-1/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-1/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.620194</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="D2" t="n">
         <v>0.229443</v>
       </c>
       <c r="E2" t="n">
-        <v>0.76535</v>
+        <v>0.711338</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
       <c r="D3" t="n">
         <v>0.371876</v>
       </c>
       <c r="E3" t="n">
-        <v>0.838984</v>
+        <v>0.76535</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.267257</v>
+        <v>0.276042</v>
       </c>
       <c r="D4" t="n">
-        <v>0.184192</v>
+        <v>0.183618</v>
       </c>
       <c r="E4" t="n">
-        <v>0.334312</v>
+        <v>0.3424</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.334312</v>
+        <v>0.3424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.198508</v>
+        <v>0.200852</v>
       </c>
       <c r="E5" t="n">
-        <v>0.362846</v>
+        <v>0.368328</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
